--- a/artfynd/A 25537-2026 artfynd.xlsx
+++ b/artfynd/A 25537-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122500815</v>
+        <v>122500811</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775063</v>
+        <v>775047</v>
       </c>
       <c r="R2" t="n">
-        <v>7110110</v>
+        <v>7110094</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122500813</v>
+        <v>122500809</v>
       </c>
       <c r="B3" t="n">
-        <v>92237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775046</v>
+        <v>775068</v>
       </c>
       <c r="R3" t="n">
-        <v>7110093</v>
+        <v>7110107</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122500811</v>
+        <v>122500815</v>
       </c>
       <c r="B4" t="n">
-        <v>92217</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775047</v>
+        <v>775063</v>
       </c>
       <c r="R4" t="n">
-        <v>7110094</v>
+        <v>7110110</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122500812</v>
+        <v>122500813</v>
       </c>
       <c r="B5" t="n">
-        <v>92260</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775068</v>
+        <v>775046</v>
       </c>
       <c r="R5" t="n">
-        <v>7110109</v>
+        <v>7110093</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122500809</v>
+        <v>122500812</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1117,7 @@
         <v>775068</v>
       </c>
       <c r="R6" t="n">
-        <v>7110107</v>
+        <v>7110109</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,50 +1180,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122500810</v>
+        <v>122500808</v>
       </c>
       <c r="B7" t="n">
-        <v>92253</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lappverket, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775074</v>
+        <v>775120</v>
       </c>
       <c r="R7" t="n">
-        <v>7110120</v>
+        <v>7109849</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1289,7 +1263,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,12 +1288,7 @@
         <v>122599402</v>
       </c>
       <c r="B8" t="n">
-        <v>56884</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25537-2026 artfynd.xlsx
+++ b/artfynd/A 25537-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500815</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500813</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122500808</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,8 +1437,22 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>